--- a/Статистика.xlsx
+++ b/Статистика.xlsx
@@ -35,12 +35,6 @@
     <t>Казанский Университет Вычислений</t>
   </si>
   <si>
-    <t>Медицина</t>
-  </si>
-  <si>
-    <t>Московский Государственный Медицинский Университет, Тамбовский Университет Медицины, Самарский Медицинский Институт</t>
-  </si>
-  <si>
     <t>Физика</t>
   </si>
   <si>
@@ -51,6 +45,12 @@
   </si>
   <si>
     <t>Воронежский Литературно-Переводческий Университет</t>
+  </si>
+  <si>
+    <t>Медицина</t>
+  </si>
+  <si>
+    <t>Московский Государственный Медицинский Университет, Тамбовский Университет Медицины, Самарский Медицинский Институт</t>
   </si>
 </sst>
 </file>
@@ -143,13 +143,13 @@
         <v>7</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>4.329999923706055</v>
+        <v>4.539999961853027</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>8</v>
@@ -160,13 +160,13 @@
         <v>9</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>4.539999961853027</v>
+        <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>10</v>
@@ -177,13 +177,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>0.0</v>
+        <v>4.329999923706055</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>12</v>

--- a/Статистика.xlsx
+++ b/Статистика.xlsx
@@ -29,10 +29,10 @@
     <t>Названия университетов</t>
   </si>
   <si>
-    <t>Математики</t>
+    <t>Лингвисты</t>
   </si>
   <si>
-    <t>Казанский Университет Вычислений</t>
+    <t>Воронежский Литературно-Переводческий Университет</t>
   </si>
   <si>
     <t>Физика</t>
@@ -41,10 +41,10 @@
     <t>Московский Выдуманный Университет, Московский Придуманный Институт</t>
   </si>
   <si>
-    <t>Лингвисты</t>
+    <t>Математики</t>
   </si>
   <si>
-    <t>Воронежский Литературно-Переводческий Университет</t>
+    <t>Казанский Университет Вычислений</t>
   </si>
   <si>
     <t>Медицина</t>
